--- a/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
+          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
         </is>
       </c>
     </row>
@@ -11946,17 +11946,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
+          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
+          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
+          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
         </is>
       </c>
     </row>
@@ -12042,17 +12042,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室</t>
+          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
         </is>
       </c>
     </row>
@@ -12106,17 +12106,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12138,17 +12138,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12158,29 +12158,29 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
     <row r="10">
       <c r="A10" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
+          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12202,17 +12202,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12222,29 +12222,29 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
+          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
         </is>
       </c>
     </row>
     <row r="12">
       <c r="A12" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
+          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
         </is>
       </c>
     </row>
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
+          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
         </is>
       </c>
     </row>
@@ -12298,17 +12298,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
+          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
         </is>
       </c>
     </row>
@@ -12330,17 +12330,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12350,7 +12350,7 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
+          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
         </is>
       </c>
     </row>
@@ -12362,17 +12362,17 @@
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
         </is>
       </c>
     </row>
@@ -12394,17 +12394,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
+          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
         </is>
       </c>
     </row>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
+          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
         </is>
       </c>
     </row>
@@ -12458,17 +12458,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
         </is>
       </c>
     </row>
@@ -12490,17 +12490,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
+          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12522,17 +12522,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室</t>
         </is>
       </c>
     </row>
@@ -12586,17 +12586,17 @@
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
+          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -12618,17 +12618,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12650,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
+          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
         </is>
       </c>
     </row>
@@ -12687,12 +12687,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
+          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
+          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
+          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
         </is>
       </c>
     </row>
@@ -12778,17 +12778,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
+          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
         </is>
       </c>
     </row>
@@ -12810,17 +12810,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
+          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
+          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12906,17 +12906,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
+          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12958,29 +12958,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
+          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心</t>
+          <t>三亚保时捷服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄服务中心</t>
+          <t>三亚保时捷售后服务中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心 → 小鹏汽车北京亦庄服务中心</t>
+          <t>三亚保时捷服务中心 → 三亚保时捷售后服务中心</t>
         </is>
       </c>
     </row>
@@ -13012,7 +13012,7 @@
       </c>
       <c r="D36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售中心</t>
+          <t>小鹏汽车北京亦庄服务中心</t>
         </is>
       </c>
       <c r="E36" s="5" t="inlineStr">
@@ -13022,29 +13022,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心 → 小鹏汽车北京亦庄销售中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心 → 小鹏汽车北京亦庄服务中心</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷服务中心</t>
+          <t>小鹏汽车北京亦庄交付中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷售后服务中心</t>
+          <t>小鹏汽车北京亦庄销售中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷服务中心 → 三亚保时捷售后服务中心</t>
+          <t>小鹏汽车北京亦庄交付中心 → 小鹏汽车北京亦庄销售中心</t>
         </is>
       </c>
     </row>
@@ -13093,7 +13093,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清南虹广场销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•慈溪前应路</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•余慈尚时代</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13125,7 +13125,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -13135,12 +13135,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•慈溪前应路</t>
+          <t>小鹏汽车乐清南虹广场销售展厅</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•余慈尚时代</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">

--- a/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
+          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
         </is>
       </c>
     </row>
@@ -11946,17 +11946,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
+          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11998,29 +11998,29 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
+          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12030,7 +12030,7 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
+          <t>浙江省温州市龙湾区高一路178号小鹏汽车 → 浙江省温州市经济技术开发区高一路178号</t>
         </is>
       </c>
     </row>
@@ -12042,17 +12042,17 @@
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
+          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
         </is>
       </c>
     </row>
@@ -12138,17 +12138,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
+          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
         </is>
       </c>
     </row>
@@ -12170,17 +12170,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -12202,17 +12202,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
+          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
         </is>
       </c>
     </row>
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
+          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -12266,17 +12266,17 @@
       </c>
       <c r="B13" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
+          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
         </is>
       </c>
     </row>
@@ -12298,17 +12298,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
+          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -12335,12 +12335,12 @@
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12350,29 +12350,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
+          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
+          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
         </is>
       </c>
     </row>
@@ -12399,12 +12399,12 @@
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
+          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
         </is>
       </c>
     </row>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
+          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
         </is>
       </c>
     </row>
@@ -12458,17 +12458,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12478,7 +12478,7 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
+          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12490,17 +12490,17 @@
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
+          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
         </is>
       </c>
     </row>
@@ -12554,17 +12554,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12574,29 +12574,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区高一路178号小鹏汽车 → 浙江省温州市经济技术开发区高一路178号</t>
+          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
         </is>
       </c>
     </row>
@@ -12618,17 +12618,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
+          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
         </is>
       </c>
     </row>
@@ -12650,17 +12650,17 @@
       </c>
       <c r="B25" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
+          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12687,12 +12687,12 @@
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12702,29 +12702,29 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
+          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
         </is>
       </c>
     </row>
     <row r="27">
       <c r="A27" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B27" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
+          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
+          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
         </is>
       </c>
     </row>
@@ -12778,17 +12778,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
         </is>
       </c>
     </row>
@@ -12810,17 +12810,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
+          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
+          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
         </is>
       </c>
     </row>
@@ -12911,12 +12911,12 @@
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
+          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12958,7 +12958,7 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
+          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
         </is>
       </c>
     </row>

--- a/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
+++ b/report/downloads/reports/网点变化对比报告_20260810_vs_20260817.xlsx
@@ -11914,17 +11914,17 @@
       </c>
       <c r="B2" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D2" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车六安东方汽车城销售服务中心</t>
+          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E2" s="5" t="inlineStr">
@@ -11934,7 +11934,7 @@
       </c>
       <c r="F2" s="5" t="inlineStr">
         <is>
-          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
+          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
         </is>
       </c>
     </row>
@@ -11946,17 +11946,17 @@
       </c>
       <c r="B3" s="5" t="inlineStr">
         <is>
-          <t>山东</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D3" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车临沂双岭路销售服务中心</t>
+          <t>小鹏汽车南通东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E3" s="5" t="inlineStr">
@@ -11966,7 +11966,7 @@
       </c>
       <c r="F3" s="5" t="inlineStr">
         <is>
-          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
+          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
         </is>
       </c>
     </row>
@@ -11978,17 +11978,17 @@
       </c>
       <c r="B4" s="5" t="inlineStr">
         <is>
-          <t>上海</t>
+          <t>新疆</t>
         </is>
       </c>
       <c r="C4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="D4" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车上海浦东金桥销售服务中心</t>
+          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
         </is>
       </c>
       <c r="E4" s="5" t="inlineStr">
@@ -11998,7 +11998,7 @@
       </c>
       <c r="F4" s="5" t="inlineStr">
         <is>
-          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
+          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
         </is>
       </c>
     </row>
@@ -12010,17 +12010,17 @@
       </c>
       <c r="B5" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D5" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车温州龙湾销售服务中心</t>
+          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E5" s="5" t="inlineStr">
@@ -12030,29 +12030,29 @@
       </c>
       <c r="F5" s="5" t="inlineStr">
         <is>
-          <t>浙江省温州市龙湾区高一路178号小鹏汽车 → 浙江省温州市经济技术开发区高一路178号</t>
+          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B6" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="D6" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
+          <t>上汽奥迪广州枫兴用户中心</t>
         </is>
       </c>
       <c r="E6" s="5" t="inlineStr">
@@ -12062,7 +12062,7 @@
       </c>
       <c r="F6" s="5" t="inlineStr">
         <is>
-          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
+          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
         </is>
       </c>
     </row>
@@ -12074,17 +12074,17 @@
       </c>
       <c r="B7" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="D7" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
+          <t>小鹏汽车榆林青云路销售服务中心</t>
         </is>
       </c>
       <c r="E7" s="5" t="inlineStr">
@@ -12094,7 +12094,7 @@
       </c>
       <c r="F7" s="5" t="inlineStr">
         <is>
-          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
+          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
         </is>
       </c>
     </row>
@@ -12106,17 +12106,17 @@
       </c>
       <c r="B8" s="5" t="inlineStr">
         <is>
-          <t>宁夏</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="D8" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
+          <t>小鹏汽车扬州国际汽车城服务中心</t>
         </is>
       </c>
       <c r="E8" s="5" t="inlineStr">
@@ -12126,7 +12126,7 @@
       </c>
       <c r="F8" s="5" t="inlineStr">
         <is>
-          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
+          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
         </is>
       </c>
     </row>
@@ -12138,17 +12138,17 @@
       </c>
       <c r="B9" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="D9" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车广州白云销售服务中心</t>
+          <t>小鹏汽车海宁城北销售服务中心</t>
         </is>
       </c>
       <c r="E9" s="5" t="inlineStr">
@@ -12158,7 +12158,7 @@
       </c>
       <c r="F9" s="5" t="inlineStr">
         <is>
-          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
+          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
         </is>
       </c>
     </row>
@@ -12170,17 +12170,17 @@
       </c>
       <c r="B10" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>陕西</t>
         </is>
       </c>
       <c r="C10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D10" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车海宁城北销售服务中心</t>
+          <t>小鹏汽车咸阳北上召汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E10" s="5" t="inlineStr">
@@ -12190,7 +12190,7 @@
       </c>
       <c r="F10" s="5" t="inlineStr">
         <is>
-          <t>浙江省嘉兴市海宁市海昌街道海宁经济开发区文苑路483号-1 → 浙江省海宁市海昌街道海宁经济技术开发区文苑路483号-1</t>
+          <t>陕西省咸阳市秦皇北路秦楚汽车城商管中心1层东、西展厅 → 陕西省咸阳市秦皇北路秦楚汽车城商管中心1层</t>
         </is>
       </c>
     </row>
@@ -12202,17 +12202,17 @@
       </c>
       <c r="B11" s="5" t="inlineStr">
         <is>
-          <t>甘肃</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D11" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
+          <t>小鹏汽车六安东方汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E11" s="5" t="inlineStr">
@@ -12222,7 +12222,7 @@
       </c>
       <c r="F11" s="5" t="inlineStr">
         <is>
-          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
+          <t>安徽省六安市金安区金安经济开发区长江东路A52号 → 安徽省六安市小鹏汽车东方汽车城皖西大道A52号</t>
         </is>
       </c>
     </row>
@@ -12234,17 +12234,17 @@
       </c>
       <c r="B12" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>上海</t>
         </is>
       </c>
       <c r="C12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="D12" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车榆林青云路销售服务中心</t>
+          <t>小鹏汽车上海浦东金桥销售服务中心</t>
         </is>
       </c>
       <c r="E12" s="5" t="inlineStr">
@@ -12254,7 +12254,7 @@
       </c>
       <c r="F12" s="5" t="inlineStr">
         <is>
-          <t>陕西省榆林市榆阳区产业四路与青云二路交汇处 → 榆阳区产业四路与青云二路交汇处</t>
+          <t>上海市浦东新区新金桥路999号4幢1层111室 → 上海市浦东新区金湘路500号 2号门 一层</t>
         </is>
       </c>
     </row>
@@ -12271,12 +12271,12 @@
       </c>
       <c r="C13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="D13" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
+          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
         </is>
       </c>
       <c r="E13" s="5" t="inlineStr">
@@ -12286,7 +12286,7 @@
       </c>
       <c r="F13" s="5" t="inlineStr">
         <is>
-          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
+          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室</t>
         </is>
       </c>
     </row>
@@ -12298,17 +12298,17 @@
       </c>
       <c r="B14" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="D14" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
+          <t>小鹏汽车南京江北新区销售服务中心</t>
         </is>
       </c>
       <c r="E14" s="5" t="inlineStr">
@@ -12318,7 +12318,7 @@
       </c>
       <c r="F14" s="5" t="inlineStr">
         <is>
-          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
+          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
         </is>
       </c>
     </row>
@@ -12330,17 +12330,17 @@
       </c>
       <c r="B15" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="D15" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
+          <t>小鹏汽车无锡锡东销售服务中心</t>
         </is>
       </c>
       <c r="E15" s="5" t="inlineStr">
@@ -12350,29 +12350,29 @@
       </c>
       <c r="F15" s="5" t="inlineStr">
         <is>
-          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
+          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
         </is>
       </c>
     </row>
     <row r="16">
       <c r="A16" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B16" s="5" t="inlineStr">
         <is>
-          <t>湖北</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="D16" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪武汉元泽新奥用户中心</t>
+          <t>小鹏汽车温州龙湾销售服务中心</t>
         </is>
       </c>
       <c r="E16" s="5" t="inlineStr">
@@ -12382,7 +12382,7 @@
       </c>
       <c r="F16" s="5" t="inlineStr">
         <is>
-          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
+          <t>浙江省温州市龙湾区高一路178号小鹏汽车 → 浙江省温州市经济技术开发区高一路178号</t>
         </is>
       </c>
     </row>
@@ -12394,17 +12394,17 @@
       </c>
       <c r="B17" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>河南</t>
         </is>
       </c>
       <c r="C17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="D17" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京江北新区销售服务中心</t>
+          <t>小鹏汽车周口南环销售服务中心</t>
         </is>
       </c>
       <c r="E17" s="5" t="inlineStr">
@@ -12414,7 +12414,7 @@
       </c>
       <c r="F17" s="5" t="inlineStr">
         <is>
-          <t>南京市江北新区泰山街道沿山东路9-8 → 南京市江北新区泰山街道沿山东路9-8号</t>
+          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
         </is>
       </c>
     </row>
@@ -12426,17 +12426,17 @@
       </c>
       <c r="B18" s="5" t="inlineStr">
         <is>
-          <t>陕西</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D18" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车宝鸡高新汽车城销售服务中心</t>
+          <t>小鹏汽车兰州安宁汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E18" s="5" t="inlineStr">
@@ -12446,7 +12446,7 @@
       </c>
       <c r="F18" s="5" t="inlineStr">
         <is>
-          <t>宝鸡市渭滨区高新十二路19号 → 陕西省宝鸡市高新开发区八鱼镇十二路19号（东风本田4S店右侧）</t>
+          <t>甘肃省兰州市安宁区北滨河西路兰州金岛智鹏汽车销售服务有限公司 → 甘肃省兰州市安宁区北滨河西路1746号安宁汽车城15号</t>
         </is>
       </c>
     </row>
@@ -12458,17 +12458,17 @@
       </c>
       <c r="B19" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="D19" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州国际汽车城服务中心</t>
+          <t>小鹏汽车广州白云销售服务中心</t>
         </is>
       </c>
       <c r="E19" s="5" t="inlineStr">
@@ -12478,29 +12478,29 @@
       </c>
       <c r="F19" s="5" t="inlineStr">
         <is>
-          <t>扬州市邗江区名车路8号 → 中国江苏省扬州市邗江区名车路8号</t>
+          <t>广州市白云区白云大道北1399号 → 广东省广州市白云区白云大道北1399号109房</t>
         </is>
       </c>
     </row>
     <row r="20">
       <c r="A20" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>奥迪</t>
         </is>
       </c>
       <c r="B20" s="5" t="inlineStr">
         <is>
-          <t>浙江</t>
+          <t>湖北</t>
         </is>
       </c>
       <c r="C20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="D20" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车杭州西溪销售服务中心</t>
+          <t>上汽奥迪武汉元泽新奥用户中心</t>
         </is>
       </c>
       <c r="E20" s="5" t="inlineStr">
@@ -12510,7 +12510,7 @@
       </c>
       <c r="F20" s="5" t="inlineStr">
         <is>
-          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
+          <t>湖北省武汉东湖新技术开发区高新四路12号 → 湖北省武汉东湖新技术开发区高新四路12号方软科技园通讯网络研发基地5号厂房</t>
         </is>
       </c>
     </row>
@@ -12522,17 +12522,17 @@
       </c>
       <c r="B21" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D21" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通瑞力产业园销售服务中心</t>
+          <t>小鹏汽车亳州远景汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E21" s="5" t="inlineStr">
@@ -12542,7 +12542,7 @@
       </c>
       <c r="F21" s="5" t="inlineStr">
         <is>
-          <t>江苏省南通市崇川区钟秀街道五一路99号3幢B01室南通瑞力产业园交付中心 → 江苏省南通市崇川区钟秀街道五一路99号3幢B01室</t>
+          <t>安徽省亳州市经开区杜仲路与桐乡路交叉口西北侧 → 亳州市谯城区杜仲路与桐乡路交叉口北100米</t>
         </is>
       </c>
     </row>
@@ -12554,17 +12554,17 @@
       </c>
       <c r="B22" s="5" t="inlineStr">
         <is>
-          <t>内蒙古</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D22" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
+          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E22" s="5" t="inlineStr">
@@ -12574,29 +12574,29 @@
       </c>
       <c r="F22" s="5" t="inlineStr">
         <is>
-          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
+          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
         </is>
       </c>
     </row>
     <row r="23">
       <c r="A23" s="5" t="inlineStr">
         <is>
-          <t>奥迪</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B23" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C23" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D23" s="5" t="inlineStr">
         <is>
-          <t>上汽奥迪广州枫兴用户中心</t>
+          <t>小鹏汽车淮南经开区汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E23" s="5" t="inlineStr">
@@ -12606,7 +12606,7 @@
       </c>
       <c r="F23" s="5" t="inlineStr">
         <is>
-          <t>广东省广州市白云区广从一路162号枫兴汽车城内 → 广东省广州市白云区广从一路162号上汽奥迪体验中心</t>
+          <t>淮南市经开区国庆东路汽配城北门向东200米 → 安徽省淮南市经开区国庆东路汽配城北门向东200米</t>
         </is>
       </c>
     </row>
@@ -12618,17 +12618,17 @@
       </c>
       <c r="B24" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>浙江</t>
         </is>
       </c>
       <c r="C24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="D24" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
+          <t>小鹏汽车杭州西溪销售服务中心</t>
         </is>
       </c>
       <c r="E24" s="5" t="inlineStr">
@@ -12638,7 +12638,7 @@
       </c>
       <c r="F24" s="5" t="inlineStr">
         <is>
-          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
+          <t>杭州市西湖区西溪路698号一层-2 → 杭州市西湖区西溪路698 号一层-2</t>
         </is>
       </c>
     </row>
@@ -12655,12 +12655,12 @@
       </c>
       <c r="C25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="D25" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车潍坊潍州路销售服务中心</t>
+          <t>小鹏汽车临沂双岭路销售服务中心</t>
         </is>
       </c>
       <c r="E25" s="5" t="inlineStr">
@@ -12670,7 +12670,7 @@
       </c>
       <c r="F25" s="5" t="inlineStr">
         <is>
-          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
+          <t>山东省临沂市双岭路与京沪高速公路交汇处东200米 → 临沂市兰山区双岭路与京沪高速交汇处东200米远通汽车大世界院内小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12682,17 +12682,17 @@
       </c>
       <c r="B26" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>广东</t>
         </is>
       </c>
       <c r="C26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="D26" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车无锡锡东销售服务中心</t>
+          <t>小鹏汽车揭阳荣通销售服务中心</t>
         </is>
       </c>
       <c r="E26" s="5" t="inlineStr">
@@ -12702,7 +12702,7 @@
       </c>
       <c r="F26" s="5" t="inlineStr">
         <is>
-          <t>江苏省无锡市锡山区先锋中路25-6-2号 → 江苏省无锡市锡山区先锋中路25-6号</t>
+          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
         </is>
       </c>
     </row>
@@ -12719,12 +12719,12 @@
       </c>
       <c r="C27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="D27" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南通东方汽车城销售服务中心</t>
+          <t>小鹏汽车南京天元路销售服务中心</t>
         </is>
       </c>
       <c r="E27" s="5" t="inlineStr">
@@ -12734,7 +12734,7 @@
       </c>
       <c r="F27" s="5" t="inlineStr">
         <is>
-          <t>南通市开发区东方汽车城吉达路11号 → 江苏省南通市开发区吉达路11号</t>
+          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
         </is>
       </c>
     </row>
@@ -12746,17 +12746,17 @@
       </c>
       <c r="B28" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>甘肃</t>
         </is>
       </c>
       <c r="C28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="D28" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车扬州江都国际汽车城销售服务中心</t>
+          <t>小鹏汽车张掖绿舟汽车城销售中心</t>
         </is>
       </c>
       <c r="E28" s="5" t="inlineStr">
@@ -12766,7 +12766,7 @@
       </c>
       <c r="F28" s="5" t="inlineStr">
         <is>
-          <t>江苏省扬州市江都区黄海南路国际汽车城内 → 扬州市江都区黄海南路国际汽车城内311号-12  小鹏汽车4S店</t>
+          <t>甘肃省张掖市甘州区新墩镇滨河新区腾飞路与崇业路交汇处绿舟汽车城2号综合楼1层 → 甘肃省张掖市甘州区绿舟汽车城内2号楼</t>
         </is>
       </c>
     </row>
@@ -12778,17 +12778,17 @@
       </c>
       <c r="B29" s="5" t="inlineStr">
         <is>
-          <t>河南</t>
+          <t>河北</t>
         </is>
       </c>
       <c r="C29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="D29" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车周口南环销售服务中心</t>
+          <t>小鹏汽车张家口白云街销售服务中心</t>
         </is>
       </c>
       <c r="E29" s="5" t="inlineStr">
@@ -12798,7 +12798,7 @@
       </c>
       <c r="F29" s="5" t="inlineStr">
         <is>
-          <t>河南省周口市川汇区太昊西路40号 → 河南省周口市川汇区太昊路与建材路交叉口西南300米</t>
+          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
         </is>
       </c>
     </row>
@@ -12810,17 +12810,17 @@
       </c>
       <c r="B30" s="5" t="inlineStr">
         <is>
-          <t>河北</t>
+          <t>安徽</t>
         </is>
       </c>
       <c r="C30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="D30" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车张家口白云街销售服务中心</t>
+          <t>小鹏汽车滁州城南万泓美众销售服务中心</t>
         </is>
       </c>
       <c r="E30" s="5" t="inlineStr">
@@ -12830,7 +12830,7 @@
       </c>
       <c r="F30" s="5" t="inlineStr">
         <is>
-          <t>河北省张家口市经济技术开发区胜利南路105号 → 河北省张家口市桥东区胜利南路105号</t>
+          <t>安徽省滁州市南谯区醉翁西路268号 → 安徽省滁州市南谯区醉翁西路270号2号楼</t>
         </is>
       </c>
     </row>
@@ -12842,17 +12842,17 @@
       </c>
       <c r="B31" s="5" t="inlineStr">
         <is>
-          <t>广东</t>
+          <t>山东</t>
         </is>
       </c>
       <c r="C31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="D31" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车揭阳荣通销售服务中心</t>
+          <t>小鹏汽车潍坊潍州路销售服务中心</t>
         </is>
       </c>
       <c r="E31" s="5" t="inlineStr">
@@ -12862,7 +12862,7 @@
       </c>
       <c r="F31" s="5" t="inlineStr">
         <is>
-          <t>广东省揭阳市榕城区环市北路与新河路交界处荣通汽车城内 → 广东省揭阳市榕城区东石北路荣通汽车城1FA5-A6号铺位</t>
+          <t>潍坊市奎文区潍州路金宝乐园南100米路西 → 潍坊市奎文区金宝乐园南100米路西</t>
         </is>
       </c>
     </row>
@@ -12874,17 +12874,17 @@
       </c>
       <c r="B32" s="5" t="inlineStr">
         <is>
-          <t>安徽</t>
+          <t>内蒙古</t>
         </is>
       </c>
       <c r="C32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="D32" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车天长五金机电汽车城销售服务中心</t>
+          <t>小鹏汽车鄂尔多斯天骄路销售服务中心</t>
         </is>
       </c>
       <c r="E32" s="5" t="inlineStr">
@@ -12894,7 +12894,7 @@
       </c>
       <c r="F32" s="5" t="inlineStr">
         <is>
-          <t>天长市炳辉路北侧、秦栏路东侧66号（北京现代天长环圣4S店旁） → 安徽省天长市炳辉路北侧秦栏路东侧北京现代天长环圣4S店旁</t>
+          <t>内蒙古鄂尔多斯市东胜区原和平宴会城北墙底商小鹏汽车交付中心 → 鄂尔多斯市康巴什区碳中和研究院内小鹏汽车</t>
         </is>
       </c>
     </row>
@@ -12906,17 +12906,17 @@
       </c>
       <c r="B33" s="5" t="inlineStr">
         <is>
-          <t>江苏</t>
+          <t>宁夏</t>
         </is>
       </c>
       <c r="C33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D33" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车南京天元路销售服务中心</t>
+          <t>小鹏汽车吴忠国际汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E33" s="5" t="inlineStr">
@@ -12926,7 +12926,7 @@
       </c>
       <c r="F33" s="5" t="inlineStr">
         <is>
-          <t>南京市江宁区天元中路123号 → 江苏省南京市江宁区天元中路123号(小龙湾地铁站出入口旁)</t>
+          <t>宁夏省吴忠市利通区东塔乡吴忠国际汽车城内小鹏汽车销售服务中心 → 宁夏回族自治区吴忠市利通区国际汽车内小鹏汽车吴忠国际汽车城店</t>
         </is>
       </c>
     </row>
@@ -12938,17 +12938,17 @@
       </c>
       <c r="B34" s="5" t="inlineStr">
         <is>
-          <t>新疆</t>
+          <t>江苏</t>
         </is>
       </c>
       <c r="C34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="D34" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乌鲁木齐赛博特车城销售展厅</t>
+          <t>小鹏汽车南京溧水汽车城销售服务中心</t>
         </is>
       </c>
       <c r="E34" s="5" t="inlineStr">
@@ -12958,29 +12958,29 @@
       </c>
       <c r="F34" s="5" t="inlineStr">
         <is>
-          <t>乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城C9-2-01 → 乌鲁木齐市鲤鱼山北路1号新疆赛博特国际汽车城圆展厅旁</t>
+          <t>南京市溧水区经济开发区群力大道7号溧水小鹏 → 南京市溧水区经济开发区群力大道7号</t>
         </is>
       </c>
     </row>
     <row r="35">
       <c r="A35" s="5" t="inlineStr">
         <is>
-          <t>保时捷</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B35" s="5" t="inlineStr">
         <is>
-          <t>海南</t>
+          <t>北京</t>
         </is>
       </c>
       <c r="C35" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心</t>
         </is>
       </c>
       <c r="D35" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷售后服务中心</t>
+          <t>小鹏汽车北京亦庄销售中心</t>
         </is>
       </c>
       <c r="E35" s="5" t="inlineStr">
@@ -12990,7 +12990,7 @@
       </c>
       <c r="F35" s="5" t="inlineStr">
         <is>
-          <t>三亚保时捷服务中心 → 三亚保时捷售后服务中心</t>
+          <t>小鹏汽车北京亦庄销售服务中心 → 小鹏汽车北京亦庄销售中心</t>
         </is>
       </c>
     </row>
@@ -13007,7 +13007,7 @@
       </c>
       <c r="C36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心</t>
+          <t>小鹏汽车北京亦庄交付中心</t>
         </is>
       </c>
       <c r="D36" s="5" t="inlineStr">
@@ -13022,29 +13022,29 @@
       </c>
       <c r="F36" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售服务中心 → 小鹏汽车北京亦庄服务中心</t>
+          <t>小鹏汽车北京亦庄交付中心 → 小鹏汽车北京亦庄服务中心</t>
         </is>
       </c>
     </row>
     <row r="37">
       <c r="A37" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>保时捷</t>
         </is>
       </c>
       <c r="B37" s="5" t="inlineStr">
         <is>
-          <t>北京</t>
+          <t>海南</t>
         </is>
       </c>
       <c r="C37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心</t>
+          <t>三亚保时捷服务中心</t>
         </is>
       </c>
       <c r="D37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄销售中心</t>
+          <t>三亚保时捷售后服务中心</t>
         </is>
       </c>
       <c r="E37" s="5" t="inlineStr">
@@ -13054,7 +13054,7 @@
       </c>
       <c r="F37" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车北京亦庄交付中心 → 小鹏汽车北京亦庄销售中心</t>
+          <t>三亚保时捷服务中心 → 三亚保时捷售后服务中心</t>
         </is>
       </c>
     </row>
@@ -13093,7 +13093,7 @@
     <row r="39">
       <c r="A39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行</t>
+          <t>小鹏</t>
         </is>
       </c>
       <c r="B39" s="5" t="inlineStr">
@@ -13103,12 +13103,12 @@
       </c>
       <c r="C39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•慈溪前应路</t>
+          <t>小鹏汽车乐清南虹广场销售展厅</t>
         </is>
       </c>
       <c r="D39" s="5" t="inlineStr">
         <is>
-          <t>鸿蒙智行尚界用户中心•余慈尚时代</t>
+          <t>小鹏汽车乐清正大广场销售展厅</t>
         </is>
       </c>
       <c r="E39" s="5" t="inlineStr">
@@ -13125,7 +13125,7 @@
     <row r="40">
       <c r="A40" s="5" t="inlineStr">
         <is>
-          <t>小鹏</t>
+          <t>鸿蒙智行</t>
         </is>
       </c>
       <c r="B40" s="5" t="inlineStr">
@@ -13135,12 +13135,12 @@
       </c>
       <c r="C40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清南虹广场销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•慈溪前应路</t>
         </is>
       </c>
       <c r="D40" s="5" t="inlineStr">
         <is>
-          <t>小鹏汽车乐清正大广场销售展厅</t>
+          <t>鸿蒙智行尚界用户中心•余慈尚时代</t>
         </is>
       </c>
       <c r="E40" s="5" t="inlineStr">
